--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260729.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260729.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>551,661,401</t>
+          <t>558,850,461</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>59.92%</t>
+          <t>60.16%</t>
         </is>
       </c>
     </row>
@@ -633,56 +633,56 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>33,259,303</t>
+          <t>33,688,223</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>5.25%</t>
+          <t>5.19%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>43,582,984</t>
+          <t>279,283,491</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.28%</t>
+          <t>3.24%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>275,525,486</t>
+          <t>44,168,504</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.23%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>74,897,855</t>
+          <t>75,902,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>263,759,795</t>
+          <t>267,201,775</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.34%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>6,562,635</t>
+          <t>6,647,950</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.33%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>400,591,735</t>
+          <t>405,775,375</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>188,261,141</t>
+          <t>190,828,281</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>11,205,398</t>
+          <t>11,351,168</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>29,763,821</t>
+          <t>30,170,106</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
@@ -853,51 +853,51 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>215,165,395</t>
+          <t>218,100,660</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>35,589,792</t>
+          <t>60,479,389</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>59,665,689</t>
+          <t>36,054,222</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>529,015,578</t>
+          <t>536,110,178</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -941,29 +941,29 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>111,248,730</t>
+          <t>112,701,910</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>8,316,172</t>
+          <t>252,407,633</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -975,39 +975,39 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>7,227,124</t>
+          <t>8,428,652</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>249,013,798</t>
+          <t>7,321,479</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>266,653,950</t>
+          <t>270,291,695</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.66%</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>342,971,167</t>
+          <t>347,650,267</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2,348,924</t>
+          <t>2,379,434</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
@@ -1095,78 +1095,78 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>86,075,426</t>
+          <t>87,248,906</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>296,612,985</t>
+          <t>15,434,449</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>68,124,666</t>
+          <t>300,335,590</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>15,226,569</t>
+          <t>69,053,671</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
@@ -1183,73 +1183,73 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>355,356,025</t>
+          <t>360,203,150</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>25,737,970</t>
+          <t>70,744,111</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>69,792,636</t>
+          <t>26,088,145</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>1,244,724</t>
+          <t>256,125,192</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,44 +1261,44 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>4,033,290</t>
+          <t>1,261,544</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>252,678,507</t>
+          <t>113,002,975</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
@@ -1315,56 +1315,56 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>207,402,993</t>
+          <t>210,232,558</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>44,124,423</t>
+          <t>4,087,835</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>111,482,275</t>
+          <t>44,726,288</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
@@ -1381,29 +1381,29 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>2,117,700</t>
+          <t>2,146,385</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,286,420</t>
+          <t>17,441,636</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,39 +1415,39 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>17,206,766</t>
+          <t>1,303,805</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.33%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>1,811,830</t>
+          <t>1,990,870</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,39 +1459,39 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>1,965,445</t>
+          <t>239,397,768</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>7,753,954</t>
+          <t>1,834,995</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,66 +1503,66 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>25,757,229</t>
+          <t>10,542,860</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.28%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>236,175,913</t>
+          <t>7,859,089</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.28%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>10,401,260</t>
+          <t>26,107,969</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
@@ -1591,44 +1591,44 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>1,779,256</t>
+          <t>24,883,955</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>24,508,600</t>
+          <t>1,803,421</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>4,831,930</t>
+          <t>4,897,645</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
@@ -1667,12 +1667,12 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>40,023,000</t>
+          <t>40,569,190</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>31,881,923</t>
+          <t>32,316,893</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.18%</t>
         </is>
       </c>
     </row>
@@ -1711,12 +1711,12 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>25,884,767</t>
+          <t>26,237,202</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>868</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.04%</t>
         </is>
       </c>
     </row>
